--- a/_vault_setup/01_md_convert/tech_yt_md_convert.xlsx
+++ b/_vault_setup/01_md_convert/tech_yt_md_convert.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vault\Koreanwithji_vault\_vault_setup\01_md_convert\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vault\koreanwithji_vault\_vault_setup\01_md_convert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A5D1F8-0FEA-4CCF-BC1E-AA96B4D8CE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92649F27-E958-4410-9669-C8C124D8D20E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="70">
   <si>
     <t>자료구분</t>
   </si>
@@ -193,6 +193,54 @@
   </si>
   <si>
     <t>Obsidian in 24 Minutes</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/kZPtAF96QD4?feature=share</t>
+  </si>
+  <si>
+    <t>raycfu</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>06_ai_video</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>How to do motion design with Claude Opus 5.5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtu.be/Xdy1vkhSz-M</t>
+  </si>
+  <si>
+    <t>Riley Brown</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Codex Just Replaced 1,000 Hours of Video Editing Tutorials</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtu.be/v7ZSa_7xjxk</t>
+  </si>
+  <si>
+    <t>How to Clone Yourself for AI Avatars</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jonathan Acuña - Doctor AI</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtu.be/xUdKBqP81k8</t>
+  </si>
+  <si>
+    <t>My AI Avatar Clone is So Realistic It Replaced Me</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dan Kieft</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -200,7 +248,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,6 +340,15 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -323,7 +380,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -372,6 +429,15 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -390,7 +456,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -489,13 +555,20 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -816,18 +889,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.7"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.09765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.08203125" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.5" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.5" style="4" customWidth="1"/>
-    <col min="4" max="4" width="113.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.09765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="95.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.08203125" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.25" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -847,7 +920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.7">
+    <row r="2" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="17" t="s">
         <v>6</v>
       </c>
@@ -867,7 +940,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.7">
+    <row r="3" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A3" s="6" t="s">
         <v>6</v>
       </c>
@@ -887,7 +960,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.7">
+    <row r="4" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="29" t="s">
         <v>6</v>
       </c>
@@ -907,7 +980,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.7">
+    <row r="5" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A5" s="30" t="s">
         <v>6</v>
       </c>
@@ -927,7 +1000,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.7">
+    <row r="6" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A6" s="30" t="s">
         <v>6</v>
       </c>
@@ -947,7 +1020,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.7">
+    <row r="7" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A7" s="30" t="s">
         <v>6</v>
       </c>
@@ -967,7 +1040,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.7">
+    <row r="8" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A8" s="30" t="s">
         <v>6</v>
       </c>
@@ -987,7 +1060,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.7">
+    <row r="9" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A9" s="6" t="s">
         <v>6</v>
       </c>
@@ -1007,7 +1080,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.7">
+    <row r="10" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A10" s="6" t="s">
         <v>6</v>
       </c>
@@ -1027,7 +1100,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.7">
+    <row r="11" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A11" s="6" t="s">
         <v>6</v>
       </c>
@@ -1047,7 +1120,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="12" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="6" t="s">
         <v>6</v>
       </c>
@@ -1067,7 +1140,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.7">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="6" t="s">
         <v>6</v>
       </c>
@@ -1087,7 +1160,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.7">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="6" t="s">
         <v>6</v>
       </c>
@@ -1107,7 +1180,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.7">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="6" t="s">
         <v>6</v>
       </c>
@@ -1127,7 +1200,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.7">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="6" t="s">
         <v>6</v>
       </c>
@@ -1147,23 +1220,103 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.7">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="35" t="s">
+      <c r="B17" s="34" t="s">
         <v>55</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="36" t="s">
+      <c r="D17" s="32" t="s">
         <v>56</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F17" s="34" t="s">
+      <c r="F17" s="33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A18" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19" s="36" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" s="36" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21" s="36" t="s">
         <v>54</v>
       </c>
     </row>
